--- a/Lampiran Dataset ASA.xlsx
+++ b/Lampiran Dataset ASA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undipmail-my.sharepoint.com/personal/dianberlianhutasoit_students_undip_ac_id/Documents/0. SEMESTER 4/MATERI/ASA/0. PROYEK INDIV ASA/KODE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{A6ADF15E-2483-4373-9E04-766FE55F3D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A85861ED-5382-4F8A-882A-8BB1FAA27BB7}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{A6ADF15E-2483-4373-9E04-766FE55F3D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6669DBB6-6BB2-4124-832F-9EFB69424B1C}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1896" yWindow="3036" windowWidth="17280" windowHeight="8880" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rubrik" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="178">
   <si>
     <t>Atribut</t>
   </si>
@@ -67,9 +67,6 @@
     <t>Jumlah Aktivitas</t>
   </si>
   <si>
-    <t>Batas Waktu (Pomodoro)</t>
-  </si>
-  <si>
     <t>Kapasitas Fokus</t>
   </si>
   <si>
@@ -551,13 +548,25 @@
   </si>
   <si>
     <t>A4, A9, A17, A25, A27, A29, A34, A37, A47, A48, A49, A50</t>
+  </si>
+  <si>
+    <t>8 blok Pomodoro</t>
+  </si>
+  <si>
+    <t>16 blok Pomodoro</t>
+  </si>
+  <si>
+    <t>24 blok Pomodoro</t>
+  </si>
+  <si>
+    <t>Batas Waktu Belajar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -609,6 +618,17 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -759,7 +779,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -830,7 +850,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -847,6 +866,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2699,7 +2725,7 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Skenario" dataDxfId="34"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Jumlah Aktivitas" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Batas Waktu (Pomodoro)" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Batas Waktu Belajar" dataDxfId="32"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Kapasitas Fokus" dataDxfId="31"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Tujuan Skenario" dataDxfId="30"/>
   </tableColumns>
@@ -2927,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2938,7 +2964,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2949,7 +2975,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2960,7 +2986,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2971,7 +2997,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2979,10 +3005,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2990,10 +3016,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3001,10 +3027,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3012,10 +3038,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3023,10 +3049,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3034,10 +3060,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3048,7 +3074,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3059,7 +3085,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3070,7 +3096,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3105,64 +3131,64 @@
         <v>12</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B2" s="10">
         <v>10</v>
       </c>
-      <c r="C2" s="10">
-        <v>8</v>
+      <c r="C2" s="10" t="s">
+        <v>174</v>
       </c>
       <c r="D2" s="10">
         <v>18</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B3" s="10">
         <v>30</v>
       </c>
-      <c r="C3" s="10">
-        <v>16</v>
+      <c r="C3" s="10" t="s">
+        <v>175</v>
       </c>
       <c r="D3" s="10">
         <v>36</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B4" s="12">
         <v>50</v>
       </c>
-      <c r="C4" s="12">
-        <v>24</v>
+      <c r="C4" s="12" t="s">
+        <v>176</v>
       </c>
       <c r="D4" s="12">
         <v>54</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -3187,10 +3213,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.6">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -3204,10 +3230,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="C2" s="5">
         <v>2</v>
@@ -3221,10 +3247,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="C3" s="5">
         <v>1</v>
@@ -3238,10 +3264,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="C4" s="5">
         <v>1</v>
@@ -3255,10 +3281,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="C5" s="5">
         <v>2</v>
@@ -3272,10 +3298,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="C6" s="5">
         <v>2</v>
@@ -3289,10 +3315,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="C7" s="5">
         <v>3</v>
@@ -3306,10 +3332,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="C8" s="5">
         <v>3</v>
@@ -3323,10 +3349,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="C9" s="5">
         <v>1</v>
@@ -3340,10 +3366,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="C10" s="5">
         <v>2</v>
@@ -3357,10 +3383,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="C11" s="7">
         <v>2</v>
@@ -3394,10 +3420,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.6">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -3411,10 +3437,10 @@
     </row>
     <row r="2" spans="1:5" ht="14.4">
       <c r="A2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="C2" s="8">
         <v>2</v>
@@ -3428,10 +3454,10 @@
     </row>
     <row r="3" spans="1:5" ht="14.4">
       <c r="A3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="C3" s="8">
         <v>1</v>
@@ -3445,10 +3471,10 @@
     </row>
     <row r="4" spans="1:5" ht="14.4">
       <c r="A4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="C4" s="8">
         <v>1</v>
@@ -3462,10 +3488,10 @@
     </row>
     <row r="5" spans="1:5" ht="14.4">
       <c r="A5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="C5" s="8">
         <v>2</v>
@@ -3479,10 +3505,10 @@
     </row>
     <row r="6" spans="1:5" ht="14.4">
       <c r="A6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="C6" s="8">
         <v>2</v>
@@ -3496,10 +3522,10 @@
     </row>
     <row r="7" spans="1:5" ht="14.4">
       <c r="A7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="C7" s="8">
         <v>3</v>
@@ -3513,10 +3539,10 @@
     </row>
     <row r="8" spans="1:5" ht="14.4">
       <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="C8" s="8">
         <v>3</v>
@@ -3530,10 +3556,10 @@
     </row>
     <row r="9" spans="1:5" ht="14.4">
       <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="C9" s="8">
         <v>1</v>
@@ -3547,10 +3573,10 @@
     </row>
     <row r="10" spans="1:5" ht="14.4">
       <c r="A10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="C10" s="8">
         <v>2</v>
@@ -3564,10 +3590,10 @@
     </row>
     <row r="11" spans="1:5" ht="14.4">
       <c r="A11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>38</v>
       </c>
       <c r="C11" s="8">
         <v>2</v>
@@ -3581,10 +3607,10 @@
     </row>
     <row r="12" spans="1:5" ht="14.4">
       <c r="A12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>40</v>
       </c>
       <c r="C12" s="8">
         <v>2</v>
@@ -3598,10 +3624,10 @@
     </row>
     <row r="13" spans="1:5" ht="14.4">
       <c r="A13" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="8">
         <v>3</v>
@@ -3615,10 +3641,10 @@
     </row>
     <row r="14" spans="1:5" ht="14.4">
       <c r="A14" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C14" s="8">
         <v>3</v>
@@ -3632,10 +3658,10 @@
     </row>
     <row r="15" spans="1:5" ht="14.4">
       <c r="A15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="C15" s="8">
         <v>2</v>
@@ -3649,10 +3675,10 @@
     </row>
     <row r="16" spans="1:5" ht="14.4">
       <c r="A16" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C16" s="8">
         <v>2</v>
@@ -3666,10 +3692,10 @@
     </row>
     <row r="17" spans="1:5" ht="14.4">
       <c r="A17" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" s="8">
         <v>3</v>
@@ -3683,10 +3709,10 @@
     </row>
     <row r="18" spans="1:5" ht="14.4">
       <c r="A18" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C18" s="8">
         <v>2</v>
@@ -3700,10 +3726,10 @@
     </row>
     <row r="19" spans="1:5" ht="14.4">
       <c r="A19" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C19" s="8">
         <v>2</v>
@@ -3717,10 +3743,10 @@
     </row>
     <row r="20" spans="1:5" ht="14.4">
       <c r="A20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="C20" s="8">
         <v>2</v>
@@ -3734,10 +3760,10 @@
     </row>
     <row r="21" spans="1:5" ht="14.4">
       <c r="A21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="C21" s="8">
         <v>2</v>
@@ -3751,10 +3777,10 @@
     </row>
     <row r="22" spans="1:5" ht="14.4">
       <c r="A22" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C22" s="8">
         <v>3</v>
@@ -3768,10 +3794,10 @@
     </row>
     <row r="23" spans="1:5" ht="27.6">
       <c r="A23" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C23" s="8">
         <v>3</v>
@@ -3785,10 +3811,10 @@
     </row>
     <row r="24" spans="1:5" ht="14.4">
       <c r="A24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="C24" s="8">
         <v>3</v>
@@ -3802,10 +3828,10 @@
     </row>
     <row r="25" spans="1:5" ht="27.6">
       <c r="A25" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C25" s="8">
         <v>2</v>
@@ -3819,10 +3845,10 @@
     </row>
     <row r="26" spans="1:5" ht="14.4">
       <c r="A26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>59</v>
       </c>
       <c r="C26" s="8">
         <v>2</v>
@@ -3836,10 +3862,10 @@
     </row>
     <row r="27" spans="1:5" ht="14.4">
       <c r="A27" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="C27" s="8">
         <v>2</v>
@@ -3853,10 +3879,10 @@
     </row>
     <row r="28" spans="1:5" ht="14.4">
       <c r="A28" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="C28" s="8">
         <v>1</v>
@@ -3870,10 +3896,10 @@
     </row>
     <row r="29" spans="1:5" ht="14.4">
       <c r="A29" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="C29" s="8">
         <v>3</v>
@@ -3887,10 +3913,10 @@
     </row>
     <row r="30" spans="1:5" ht="14.4">
       <c r="A30" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="C30" s="8">
         <v>1</v>
@@ -3904,10 +3930,10 @@
     </row>
     <row r="31" spans="1:5" ht="27.6">
       <c r="A31" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>68</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>69</v>
       </c>
       <c r="C31" s="8">
         <v>2</v>
@@ -3941,10 +3967,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.6">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -3958,10 +3984,10 @@
     </row>
     <row r="2" spans="1:5" ht="14.4">
       <c r="A2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="C2" s="8">
         <v>2</v>
@@ -3975,10 +4001,10 @@
     </row>
     <row r="3" spans="1:5" ht="14.4">
       <c r="A3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="C3" s="8">
         <v>1</v>
@@ -3992,10 +4018,10 @@
     </row>
     <row r="4" spans="1:5" ht="14.4">
       <c r="A4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="C4" s="8">
         <v>1</v>
@@ -4009,10 +4035,10 @@
     </row>
     <row r="5" spans="1:5" ht="14.4">
       <c r="A5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="C5" s="8">
         <v>2</v>
@@ -4026,10 +4052,10 @@
     </row>
     <row r="6" spans="1:5" ht="14.4">
       <c r="A6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="C6" s="8">
         <v>2</v>
@@ -4043,10 +4069,10 @@
     </row>
     <row r="7" spans="1:5" ht="14.4">
       <c r="A7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="C7" s="8">
         <v>3</v>
@@ -4060,10 +4086,10 @@
     </row>
     <row r="8" spans="1:5" ht="14.4">
       <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="C8" s="8">
         <v>3</v>
@@ -4077,10 +4103,10 @@
     </row>
     <row r="9" spans="1:5" ht="14.4">
       <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="C9" s="8">
         <v>1</v>
@@ -4094,10 +4120,10 @@
     </row>
     <row r="10" spans="1:5" ht="14.4">
       <c r="A10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="C10" s="8">
         <v>2</v>
@@ -4111,10 +4137,10 @@
     </row>
     <row r="11" spans="1:5" ht="14.4">
       <c r="A11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>38</v>
       </c>
       <c r="C11" s="8">
         <v>2</v>
@@ -4128,10 +4154,10 @@
     </row>
     <row r="12" spans="1:5" ht="14.4">
       <c r="A12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>40</v>
       </c>
       <c r="C12" s="8">
         <v>2</v>
@@ -4145,10 +4171,10 @@
     </row>
     <row r="13" spans="1:5" ht="14.4">
       <c r="A13" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="8">
         <v>3</v>
@@ -4162,10 +4188,10 @@
     </row>
     <row r="14" spans="1:5" ht="14.4">
       <c r="A14" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C14" s="8">
         <v>3</v>
@@ -4179,10 +4205,10 @@
     </row>
     <row r="15" spans="1:5" ht="14.4">
       <c r="A15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="C15" s="8">
         <v>2</v>
@@ -4196,10 +4222,10 @@
     </row>
     <row r="16" spans="1:5" ht="14.4">
       <c r="A16" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C16" s="8">
         <v>2</v>
@@ -4213,10 +4239,10 @@
     </row>
     <row r="17" spans="1:5" ht="14.4">
       <c r="A17" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" s="8">
         <v>3</v>
@@ -4230,10 +4256,10 @@
     </row>
     <row r="18" spans="1:5" ht="14.4">
       <c r="A18" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C18" s="8">
         <v>2</v>
@@ -4247,10 +4273,10 @@
     </row>
     <row r="19" spans="1:5" ht="14.4">
       <c r="A19" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C19" s="8">
         <v>2</v>
@@ -4264,10 +4290,10 @@
     </row>
     <row r="20" spans="1:5" ht="14.4">
       <c r="A20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="C20" s="8">
         <v>2</v>
@@ -4281,10 +4307,10 @@
     </row>
     <row r="21" spans="1:5" ht="14.4">
       <c r="A21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="C21" s="8">
         <v>2</v>
@@ -4298,10 +4324,10 @@
     </row>
     <row r="22" spans="1:5" ht="14.4">
       <c r="A22" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C22" s="8">
         <v>3</v>
@@ -4315,10 +4341,10 @@
     </row>
     <row r="23" spans="1:5" ht="27.6">
       <c r="A23" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C23" s="8">
         <v>3</v>
@@ -4332,10 +4358,10 @@
     </row>
     <row r="24" spans="1:5" ht="14.4">
       <c r="A24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="C24" s="8">
         <v>3</v>
@@ -4349,10 +4375,10 @@
     </row>
     <row r="25" spans="1:5" ht="27.6">
       <c r="A25" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C25" s="8">
         <v>2</v>
@@ -4366,10 +4392,10 @@
     </row>
     <row r="26" spans="1:5" ht="14.4">
       <c r="A26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>59</v>
       </c>
       <c r="C26" s="8">
         <v>2</v>
@@ -4383,10 +4409,10 @@
     </row>
     <row r="27" spans="1:5" ht="14.4">
       <c r="A27" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="C27" s="8">
         <v>2</v>
@@ -4400,10 +4426,10 @@
     </row>
     <row r="28" spans="1:5" ht="14.4">
       <c r="A28" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="C28" s="8">
         <v>1</v>
@@ -4417,10 +4443,10 @@
     </row>
     <row r="29" spans="1:5" ht="14.4">
       <c r="A29" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="C29" s="8">
         <v>3</v>
@@ -4434,10 +4460,10 @@
     </row>
     <row r="30" spans="1:5" ht="14.4">
       <c r="A30" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="C30" s="8">
         <v>1</v>
@@ -4451,10 +4477,10 @@
     </row>
     <row r="31" spans="1:5" ht="27.6">
       <c r="A31" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="C31" s="8">
         <v>2</v>
@@ -4468,10 +4494,10 @@
     </row>
     <row r="32" spans="1:5" ht="14.4">
       <c r="A32" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C32" s="8">
         <v>2</v>
@@ -4485,10 +4511,10 @@
     </row>
     <row r="33" spans="1:5" ht="14.4">
       <c r="A33" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="C33" s="8">
         <v>3</v>
@@ -4502,10 +4528,10 @@
     </row>
     <row r="34" spans="1:5" ht="14.4">
       <c r="A34" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="C34" s="8">
         <v>2</v>
@@ -4519,10 +4545,10 @@
     </row>
     <row r="35" spans="1:5" ht="14.4">
       <c r="A35" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="C35" s="8">
         <v>1</v>
@@ -4536,10 +4562,10 @@
     </row>
     <row r="36" spans="1:5" ht="14.4">
       <c r="A36" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C36" s="8">
         <v>2</v>
@@ -4553,10 +4579,10 @@
     </row>
     <row r="37" spans="1:5" ht="14.4">
       <c r="A37" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C37" s="8">
         <v>3</v>
@@ -4570,10 +4596,10 @@
     </row>
     <row r="38" spans="1:5" ht="14.4">
       <c r="A38" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C38" s="8">
         <v>1</v>
@@ -4587,10 +4613,10 @@
     </row>
     <row r="39" spans="1:5" ht="14.4">
       <c r="A39" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C39" s="8">
         <v>3</v>
@@ -4604,10 +4630,10 @@
     </row>
     <row r="40" spans="1:5" ht="14.4">
       <c r="A40" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C40" s="8">
         <v>3</v>
@@ -4621,10 +4647,10 @@
     </row>
     <row r="41" spans="1:5" ht="14.4">
       <c r="A41" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>83</v>
       </c>
       <c r="C41" s="8">
         <v>1</v>
@@ -4638,10 +4664,10 @@
     </row>
     <row r="42" spans="1:5" ht="14.4">
       <c r="A42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="C42" s="8">
         <v>2</v>
@@ -4655,10 +4681,10 @@
     </row>
     <row r="43" spans="1:5" ht="14.4">
       <c r="A43" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="C43" s="8">
         <v>2</v>
@@ -4672,10 +4698,10 @@
     </row>
     <row r="44" spans="1:5" ht="14.4">
       <c r="A44" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="C44" s="8">
         <v>2</v>
@@ -4689,10 +4715,10 @@
     </row>
     <row r="45" spans="1:5" ht="14.4">
       <c r="A45" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="C45" s="8">
         <v>3</v>
@@ -4706,10 +4732,10 @@
     </row>
     <row r="46" spans="1:5" ht="14.4">
       <c r="A46" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="C46" s="8">
         <v>2</v>
@@ -4723,10 +4749,10 @@
     </row>
     <row r="47" spans="1:5" ht="14.4">
       <c r="A47" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="C47" s="8">
         <v>3</v>
@@ -4740,10 +4766,10 @@
     </row>
     <row r="48" spans="1:5" ht="27.6">
       <c r="A48" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C48" s="8">
         <v>2</v>
@@ -4757,10 +4783,10 @@
     </row>
     <row r="49" spans="1:5" ht="14.4">
       <c r="A49" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="C49" s="8">
         <v>2</v>
@@ -4774,10 +4800,10 @@
     </row>
     <row r="50" spans="1:5" ht="14.4">
       <c r="A50" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C50" s="8">
         <v>1</v>
@@ -4791,10 +4817,10 @@
     </row>
     <row r="51" spans="1:5" ht="14.4">
       <c r="A51" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="C51" s="8">
         <v>1</v>
@@ -4816,7 +4842,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4832,143 +4858,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="25" customFormat="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="E1" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="G1" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="H1" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="I1" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="J1" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="I1" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="J1" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="B2" s="27">
+        <v>100</v>
+      </c>
+      <c r="C2" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="D2" s="27">
+        <v>0.01</v>
+      </c>
+      <c r="E2" s="27">
+        <v>100</v>
+      </c>
+      <c r="F2" s="27">
+        <v>326</v>
+      </c>
+      <c r="G2" s="27">
+        <v>7</v>
+      </c>
+      <c r="H2" s="27">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="28" t="s">
+      <c r="I2" s="27">
+        <v>0</v>
+      </c>
+      <c r="J2" s="27">
+        <v>31.326000000000001</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B3" s="27">
+        <v>1000</v>
+      </c>
+      <c r="C3" s="27">
+        <v>0.95</v>
+      </c>
+      <c r="D3" s="27">
+        <v>0.01</v>
+      </c>
+      <c r="E3" s="27">
         <v>100</v>
       </c>
-      <c r="C2" s="28">
-        <v>0.9</v>
-      </c>
-      <c r="D2" s="28">
+      <c r="F3" s="27">
+        <v>326</v>
+      </c>
+      <c r="G3" s="27">
+        <v>7</v>
+      </c>
+      <c r="H3" s="27">
+        <v>18</v>
+      </c>
+      <c r="I3" s="27">
+        <v>0</v>
+      </c>
+      <c r="J3" s="27">
+        <v>84.450999999999993</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="27">
+        <v>1000</v>
+      </c>
+      <c r="C4" s="27">
+        <v>0.99</v>
+      </c>
+      <c r="D4" s="27">
         <v>0.01</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E4" s="27">
         <v>100</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F4" s="27">
         <v>326</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G4" s="27">
         <v>7</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H4" s="27">
         <v>18</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I4" s="27">
         <v>0</v>
       </c>
-      <c r="J2" s="28">
-        <v>31.326000000000001</v>
-      </c>
-      <c r="K2" s="28" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="B3" s="28">
-        <v>1000</v>
-      </c>
-      <c r="C3" s="28">
-        <v>0.95</v>
-      </c>
-      <c r="D3" s="28">
-        <v>0.01</v>
-      </c>
-      <c r="E3" s="28">
-        <v>100</v>
-      </c>
-      <c r="F3" s="28">
-        <v>326</v>
-      </c>
-      <c r="G3" s="28">
-        <v>7</v>
-      </c>
-      <c r="H3" s="28">
-        <v>18</v>
-      </c>
-      <c r="I3" s="28">
-        <v>0</v>
-      </c>
-      <c r="J3" s="28">
-        <v>84.450999999999993</v>
-      </c>
-      <c r="K3" s="28" t="s">
+      <c r="J4" s="27">
+        <v>430.96899999999999</v>
+      </c>
+      <c r="K4" s="27" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="28">
-        <v>1000</v>
-      </c>
-      <c r="C4" s="28">
-        <v>0.99</v>
-      </c>
-      <c r="D4" s="28">
-        <v>0.01</v>
-      </c>
-      <c r="E4" s="28">
-        <v>100</v>
-      </c>
-      <c r="F4" s="28">
-        <v>326</v>
-      </c>
-      <c r="G4" s="28">
-        <v>7</v>
-      </c>
-      <c r="H4" s="28">
-        <v>18</v>
-      </c>
-      <c r="I4" s="28">
-        <v>0</v>
-      </c>
-      <c r="J4" s="28">
-        <v>430.96899999999999</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4978,7 +5004,7 @@
       <c r="D5" s="21"/>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
-      <c r="G5" s="26"/>
+      <c r="G5" s="32"/>
       <c r="H5" s="21"/>
       <c r="I5" s="21"/>
       <c r="J5" s="21"/>
@@ -4986,8 +5012,33 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="14" t="s">
-        <v>170</v>
-      </c>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="D12" s="21"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="21"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="D13" s="21"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="21"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="D14" s="21"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="21"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="D15" s="21"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5009,40 +5060,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="30" t="s">
         <v>116</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="G1" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="H1" s="31" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D2" s="18">
         <v>286</v>
@@ -5062,13 +5113,13 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D3" s="18">
         <v>326</v>
@@ -5088,13 +5139,13 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D4" s="18">
         <v>326</v>
@@ -5114,13 +5165,13 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D5" s="18">
         <v>686</v>
@@ -5140,13 +5191,13 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D6" s="18">
         <v>686</v>
@@ -5166,13 +5217,13 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D7" s="18">
         <v>642</v>
@@ -5192,13 +5243,13 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D8" s="18">
         <v>972</v>
@@ -5218,13 +5269,13 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D9" s="18">
         <v>1013</v>
@@ -5244,13 +5295,13 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" s="20">
         <v>954</v>
@@ -5264,7 +5315,7 @@
       <c r="G10" s="20">
         <v>185.25700000000001</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="31">
         <v>5.82</v>
       </c>
     </row>
